--- a/src/data/inland_marine_lob.xlsx
+++ b/src/data/inland_marine_lob.xlsx
@@ -1,23 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AFF0A8-8FA9-493A-B483-2897060E482E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="01_Policy_Info" sheetId="1" r:id="rId1"/>
-    <sheet name="03_IM_Equipment" sheetId="2" r:id="rId2"/>
-    <sheet name="04_IM_MiscArticles" sheetId="3" r:id="rId3"/>
-    <sheet name="05_IM_LossPayees" sheetId="4" r:id="rId4"/>
-    <sheet name="06_IM_AdditInfo" sheetId="5" r:id="rId5"/>
-    <sheet name="Test Scenario Details" sheetId="6" r:id="rId6"/>
+    <sheet sheetId="1" name="01_Policy_Info" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="03_IM_Equipment" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="04_IM_MiscArticles" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="05_IM_LossPayees" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="06_IM_AdditInfo" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Test Scenario Details" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'05_IM_LossPayees'!$A$1:$L$121</definedName>
-  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -5653,6 +5646,9 @@
     <t>4100 Roland Ave</t>
   </si>
   <si>
+    <t>Loss Payable</t>
+  </si>
+  <si>
     <t>Secondary lender on lighting kit</t>
   </si>
   <si>
@@ -5720,9 +5716,6 @@
   </si>
   <si>
     <t>88 W 100 N</t>
-  </si>
-  <si>
-    <t>Loss Payable</t>
   </si>
   <si>
     <t>Finance agreement on digital imaging equipment</t>
@@ -7420,21 +7413,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -7817,11 +7810,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS83"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="1" max="1" width="23.285714285714285" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
@@ -7834,7 +7827,7 @@
     <col min="11" max="11" width="40" customWidth="1"/>
     <col min="12" max="12" width="25" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="42.109375" customWidth="1"/>
+    <col min="14" max="14" width="42.142857142857146" customWidth="1"/>
     <col min="15" max="15" width="37" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
@@ -7846,7 +7839,7 @@
     <col min="24" max="24" width="17" customWidth="1"/>
     <col min="25" max="25" width="15" customWidth="1"/>
     <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="27" width="42.109375" customWidth="1"/>
+    <col min="27" max="27" width="42.142857142857146" customWidth="1"/>
     <col min="28" max="28" width="32" customWidth="1"/>
     <col min="29" max="29" width="16" customWidth="1"/>
     <col min="30" max="30" width="27" customWidth="1"/>
@@ -7866,7 +7859,7 @@
     <col min="45" max="45" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8003,7 +7996,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -8137,7 +8130,7 @@
         <v>19107</v>
       </c>
     </row>
-    <row r="3" spans="1:45">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -8259,7 +8252,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:45">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -8393,7 +8386,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:45">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -8515,7 +8508,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:45">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -8649,7 +8642,7 @@
         <v>75201</v>
       </c>
     </row>
-    <row r="7" spans="1:45">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>204</v>
       </c>
@@ -8771,7 +8764,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:45">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>231</v>
       </c>
@@ -8908,7 +8901,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:45">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -9030,7 +9023,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:45">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>291</v>
       </c>
@@ -9164,7 +9157,7 @@
         <v>98402</v>
       </c>
     </row>
-    <row r="11" spans="1:45">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>320</v>
       </c>
@@ -9286,7 +9279,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:45">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>344</v>
       </c>
@@ -9423,7 +9416,7 @@
         <v>53703</v>
       </c>
     </row>
-    <row r="13" spans="1:45">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>372</v>
       </c>
@@ -9545,7 +9538,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:45">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>398</v>
       </c>
@@ -9679,7 +9672,7 @@
         <v>35203</v>
       </c>
     </row>
-    <row r="15" spans="1:45">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>427</v>
       </c>
@@ -9804,7 +9797,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:45">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>454</v>
       </c>
@@ -9929,7 +9922,7 @@
         <v>85201</v>
       </c>
     </row>
-    <row r="17" spans="1:45">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>479</v>
       </c>
@@ -10054,7 +10047,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:45">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>504</v>
       </c>
@@ -10188,7 +10181,7 @@
         <v>92101</v>
       </c>
     </row>
-    <row r="19" spans="1:45">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -10310,7 +10303,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:45">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>549</v>
       </c>
@@ -10444,7 +10437,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="21" spans="1:45">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>578</v>
       </c>
@@ -10569,7 +10562,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:45">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>602</v>
       </c>
@@ -10706,7 +10699,7 @@
         <v>33602</v>
       </c>
     </row>
-    <row r="23" spans="1:45">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>627</v>
       </c>
@@ -10828,7 +10821,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:45">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>647</v>
       </c>
@@ -10965,7 +10958,7 @@
         <v>32801</v>
       </c>
     </row>
-    <row r="25" spans="1:45">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>672</v>
       </c>
@@ -11102,7 +11095,7 @@
         <v>83651</v>
       </c>
     </row>
-    <row r="26" spans="1:45">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>696</v>
       </c>
@@ -11221,7 +11214,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:45">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>718</v>
       </c>
@@ -11358,7 +11351,7 @@
         <v>46802</v>
       </c>
     </row>
-    <row r="28" spans="1:45">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>739</v>
       </c>
@@ -11483,7 +11476,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:45">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>761</v>
       </c>
@@ -11620,7 +11613,7 @@
         <v>40202</v>
       </c>
     </row>
-    <row r="30" spans="1:45">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>786</v>
       </c>
@@ -11757,7 +11750,7 @@
         <v>40507</v>
       </c>
     </row>
-    <row r="31" spans="1:45">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>812</v>
       </c>
@@ -11876,7 +11869,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:45">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>831</v>
       </c>
@@ -12013,7 +12006,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="33" spans="1:45">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>855</v>
       </c>
@@ -12138,7 +12131,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:45">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>875</v>
       </c>
@@ -12272,7 +12265,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="35" spans="1:45">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>900</v>
       </c>
@@ -12397,7 +12390,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:45">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>920</v>
       </c>
@@ -12528,7 +12521,7 @@
         <v>39501</v>
       </c>
     </row>
-    <row r="37" spans="1:45">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>943</v>
       </c>
@@ -12653,7 +12646,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:45">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>965</v>
       </c>
@@ -12790,7 +12783,7 @@
         <v>59101</v>
       </c>
     </row>
-    <row r="39" spans="1:45">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>989</v>
       </c>
@@ -12912,7 +12905,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:45">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1012</v>
       </c>
@@ -13049,7 +13042,7 @@
         <v>89701</v>
       </c>
     </row>
-    <row r="41" spans="1:45">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1037</v>
       </c>
@@ -13174,7 +13167,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:45">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1058</v>
       </c>
@@ -13311,7 +13304,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="43" spans="1:45">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1083</v>
       </c>
@@ -13430,7 +13423,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:45">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1103</v>
       </c>
@@ -13567,7 +13560,7 @@
         <v>10007</v>
       </c>
     </row>
-    <row r="45" spans="1:45">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1127</v>
       </c>
@@ -13692,7 +13685,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:45">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1148</v>
       </c>
@@ -13829,7 +13822,7 @@
         <v>58201</v>
       </c>
     </row>
-    <row r="47" spans="1:45">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1167</v>
       </c>
@@ -13954,7 +13947,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:45">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1186</v>
       </c>
@@ -14082,7 +14075,7 @@
         <v>44113</v>
       </c>
     </row>
-    <row r="49" spans="1:45">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1204</v>
       </c>
@@ -14207,7 +14200,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:45">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1226</v>
       </c>
@@ -14344,7 +14337,7 @@
         <v>97204</v>
       </c>
     </row>
-    <row r="51" spans="1:45">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1250</v>
       </c>
@@ -14463,7 +14456,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:45">
+    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1270</v>
       </c>
@@ -14600,7 +14593,7 @@
         <v>29601</v>
       </c>
     </row>
-    <row r="53" spans="1:45">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1290</v>
       </c>
@@ -14725,7 +14718,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:45">
+    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1312</v>
       </c>
@@ -14859,7 +14852,7 @@
         <v>38103</v>
       </c>
     </row>
-    <row r="55" spans="1:45">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1333</v>
       </c>
@@ -14984,7 +14977,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:45">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1353</v>
       </c>
@@ -15121,7 +15114,7 @@
         <v>84101</v>
       </c>
     </row>
-    <row r="57" spans="1:45">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1374</v>
       </c>
@@ -15243,7 +15236,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:45">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1396</v>
       </c>
@@ -15377,7 +15370,7 @@
         <v>22314</v>
       </c>
     </row>
-    <row r="59" spans="1:45">
+    <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1416</v>
       </c>
@@ -15502,7 +15495,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="1:45">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1436</v>
       </c>
@@ -15636,7 +15629,7 @@
         <v>25701</v>
       </c>
     </row>
-    <row r="61" spans="1:45">
+    <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1454</v>
       </c>
@@ -15758,98 +15751,98 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:45">
+    <row r="62" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:45">
+    <row r="63" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:45">
+    <row r="64" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="26:26">
+    <row r="65" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="26:26">
+    <row r="66" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="26:26">
+    <row r="67" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="26:26">
+    <row r="68" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="26:26">
+    <row r="69" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="26:26">
+    <row r="70" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="26:26">
+    <row r="71" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="26:26">
+    <row r="72" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="26:26">
+    <row r="73" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="26:26">
+    <row r="74" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="26:26">
+    <row r="75" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="26:26">
+    <row r="76" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="26:26">
+    <row r="77" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="26:26">
+    <row r="78" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="26:26">
+    <row r="79" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="26:26">
+    <row r="80" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="26:26">
+    <row r="81" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="26:26">
+    <row r="82" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="26:26">
+    <row r="83" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z83" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AS61"/>
   <hyperlinks>
-    <hyperlink ref="R2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AH2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="R2" r:id="rId1"/>
+    <hyperlink ref="AH2" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G295"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="9.33203125" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="1" max="2" width="9.285714285714286" customWidth="1"/>
+    <col min="3" max="3" width="42.142857142857146" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="42.109375" customWidth="1"/>
-    <col min="8" max="24" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="42.142857142857146" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15872,7 +15865,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -15895,7 +15888,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -15918,7 +15911,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -15941,7 +15934,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -15964,7 +15957,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -15987,7 +15980,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -16010,7 +16003,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -16033,7 +16026,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -16056,7 +16049,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -16079,7 +16072,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>81</v>
       </c>
@@ -16102,7 +16095,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>81</v>
       </c>
@@ -16125,7 +16118,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>81</v>
       </c>
@@ -16148,7 +16141,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -16171,7 +16164,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -16194,7 +16187,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -16217,7 +16210,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -16240,7 +16233,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>113</v>
       </c>
@@ -16263,7 +16256,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>113</v>
       </c>
@@ -16286,7 +16279,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -16309,7 +16302,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>113</v>
       </c>
@@ -16332,7 +16325,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -16355,7 +16348,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -16378,7 +16371,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>146</v>
       </c>
@@ -16401,7 +16394,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -16424,7 +16417,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>146</v>
       </c>
@@ -16447,7 +16440,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>146</v>
       </c>
@@ -16470,7 +16463,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>146</v>
       </c>
@@ -16493,7 +16486,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>146</v>
       </c>
@@ -16516,7 +16509,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>146</v>
       </c>
@@ -16539,7 +16532,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>174</v>
       </c>
@@ -16562,7 +16555,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -16585,7 +16578,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>174</v>
       </c>
@@ -16608,7 +16601,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -16631,7 +16624,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -16654,7 +16647,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>174</v>
       </c>
@@ -16677,7 +16670,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>174</v>
       </c>
@@ -16700,7 +16693,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>174</v>
       </c>
@@ -16723,7 +16716,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>174</v>
       </c>
@@ -16746,7 +16739,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>204</v>
       </c>
@@ -16769,7 +16762,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>204</v>
       </c>
@@ -16792,7 +16785,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>204</v>
       </c>
@@ -16815,7 +16808,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>204</v>
       </c>
@@ -16838,7 +16831,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>231</v>
       </c>
@@ -16861,7 +16854,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>231</v>
       </c>
@@ -16884,7 +16877,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>231</v>
       </c>
@@ -16907,7 +16900,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>231</v>
       </c>
@@ -16930,7 +16923,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>263</v>
       </c>
@@ -16953,7 +16946,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>263</v>
       </c>
@@ -16976,7 +16969,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>263</v>
       </c>
@@ -16999,7 +16992,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>263</v>
       </c>
@@ -17022,7 +17015,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>263</v>
       </c>
@@ -17045,7 +17038,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>263</v>
       </c>
@@ -17068,7 +17061,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>263</v>
       </c>
@@ -17091,7 +17084,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>263</v>
       </c>
@@ -17114,7 +17107,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>263</v>
       </c>
@@ -17137,7 +17130,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>263</v>
       </c>
@@ -17160,7 +17153,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>263</v>
       </c>
@@ -17183,7 +17176,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>263</v>
       </c>
@@ -17206,7 +17199,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>263</v>
       </c>
@@ -17229,7 +17222,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>263</v>
       </c>
@@ -17252,7 +17245,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>263</v>
       </c>
@@ -17275,7 +17268,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>263</v>
       </c>
@@ -17298,7 +17291,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>263</v>
       </c>
@@ -17321,7 +17314,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>263</v>
       </c>
@@ -17344,7 +17337,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>263</v>
       </c>
@@ -17367,7 +17360,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>263</v>
       </c>
@@ -17390,7 +17383,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>291</v>
       </c>
@@ -17413,7 +17406,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>291</v>
       </c>
@@ -17436,7 +17429,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>291</v>
       </c>
@@ -17459,7 +17452,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -17482,7 +17475,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>291</v>
       </c>
@@ -17505,7 +17498,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>320</v>
       </c>
@@ -17528,7 +17521,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>320</v>
       </c>
@@ -17551,7 +17544,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>344</v>
       </c>
@@ -17574,7 +17567,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>372</v>
       </c>
@@ -17597,7 +17590,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>372</v>
       </c>
@@ -17620,7 +17613,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>372</v>
       </c>
@@ -17643,7 +17636,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>372</v>
       </c>
@@ -17666,7 +17659,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>398</v>
       </c>
@@ -17689,7 +17682,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>398</v>
       </c>
@@ -17712,7 +17705,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>398</v>
       </c>
@@ -17735,7 +17728,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>398</v>
       </c>
@@ -17758,7 +17751,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>427</v>
       </c>
@@ -17781,7 +17774,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>427</v>
       </c>
@@ -17804,7 +17797,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>427</v>
       </c>
@@ -17827,7 +17820,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>427</v>
       </c>
@@ -17850,7 +17843,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>454</v>
       </c>
@@ -17873,7 +17866,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>454</v>
       </c>
@@ -17896,7 +17889,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>454</v>
       </c>
@@ -17919,7 +17912,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>454</v>
       </c>
@@ -17942,7 +17935,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>479</v>
       </c>
@@ -17965,7 +17958,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>479</v>
       </c>
@@ -17988,7 +17981,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>479</v>
       </c>
@@ -18011,7 +18004,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>479</v>
       </c>
@@ -18034,7 +18027,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>504</v>
       </c>
@@ -18057,7 +18050,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>504</v>
       </c>
@@ -18080,7 +18073,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>504</v>
       </c>
@@ -18103,7 +18096,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>504</v>
       </c>
@@ -18126,7 +18119,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>526</v>
       </c>
@@ -18149,7 +18142,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>526</v>
       </c>
@@ -18172,7 +18165,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>526</v>
       </c>
@@ -18195,7 +18188,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>526</v>
       </c>
@@ -18218,7 +18211,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>549</v>
       </c>
@@ -18241,7 +18234,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>549</v>
       </c>
@@ -18264,7 +18257,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>549</v>
       </c>
@@ -18287,7 +18280,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>549</v>
       </c>
@@ -18310,7 +18303,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>578</v>
       </c>
@@ -18333,7 +18326,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>578</v>
       </c>
@@ -18356,7 +18349,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>578</v>
       </c>
@@ -18379,7 +18372,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>578</v>
       </c>
@@ -18402,7 +18395,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>602</v>
       </c>
@@ -18425,7 +18418,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>602</v>
       </c>
@@ -18448,7 +18441,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>602</v>
       </c>
@@ -18471,7 +18464,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>602</v>
       </c>
@@ -18494,7 +18487,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>627</v>
       </c>
@@ -18517,7 +18510,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>627</v>
       </c>
@@ -18540,7 +18533,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>627</v>
       </c>
@@ -18563,7 +18556,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>627</v>
       </c>
@@ -18586,7 +18579,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>647</v>
       </c>
@@ -18609,7 +18602,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>647</v>
       </c>
@@ -18632,7 +18625,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>647</v>
       </c>
@@ -18655,7 +18648,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>647</v>
       </c>
@@ -18678,7 +18671,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>672</v>
       </c>
@@ -18701,7 +18694,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>672</v>
       </c>
@@ -18724,7 +18717,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>672</v>
       </c>
@@ -18747,7 +18740,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>672</v>
       </c>
@@ -18770,7 +18763,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>672</v>
       </c>
@@ -18793,7 +18786,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>672</v>
       </c>
@@ -18816,7 +18809,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>672</v>
       </c>
@@ -18839,7 +18832,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>672</v>
       </c>
@@ -18862,7 +18855,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>672</v>
       </c>
@@ -18885,7 +18878,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>672</v>
       </c>
@@ -18908,7 +18901,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>672</v>
       </c>
@@ -18931,7 +18924,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>672</v>
       </c>
@@ -18954,7 +18947,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>672</v>
       </c>
@@ -18977,7 +18970,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>672</v>
       </c>
@@ -19000,7 +18993,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>672</v>
       </c>
@@ -19023,7 +19016,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>672</v>
       </c>
@@ -19046,7 +19039,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>672</v>
       </c>
@@ -19069,7 +19062,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>696</v>
       </c>
@@ -19092,7 +19085,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>696</v>
       </c>
@@ -19115,7 +19108,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>696</v>
       </c>
@@ -19138,7 +19131,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>696</v>
       </c>
@@ -19161,7 +19154,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>718</v>
       </c>
@@ -19184,7 +19177,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>718</v>
       </c>
@@ -19207,7 +19200,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>718</v>
       </c>
@@ -19230,7 +19223,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>718</v>
       </c>
@@ -19253,7 +19246,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>739</v>
       </c>
@@ -19276,7 +19269,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>739</v>
       </c>
@@ -19299,7 +19292,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>739</v>
       </c>
@@ -19322,7 +19315,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>739</v>
       </c>
@@ -19345,7 +19338,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>761</v>
       </c>
@@ -19368,7 +19361,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>761</v>
       </c>
@@ -19391,7 +19384,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>761</v>
       </c>
@@ -19414,7 +19407,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>761</v>
       </c>
@@ -19437,7 +19430,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>786</v>
       </c>
@@ -19460,7 +19453,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>786</v>
       </c>
@@ -19483,7 +19476,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>786</v>
       </c>
@@ -19506,7 +19499,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>786</v>
       </c>
@@ -19529,7 +19522,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>786</v>
       </c>
@@ -19552,7 +19545,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>812</v>
       </c>
@@ -19575,7 +19568,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>812</v>
       </c>
@@ -19598,7 +19591,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>812</v>
       </c>
@@ -19621,7 +19614,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>812</v>
       </c>
@@ -19644,7 +19637,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>831</v>
       </c>
@@ -19667,7 +19660,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>831</v>
       </c>
@@ -19690,7 +19683,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>831</v>
       </c>
@@ -19713,7 +19706,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>831</v>
       </c>
@@ -19736,7 +19729,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>855</v>
       </c>
@@ -19759,7 +19752,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>855</v>
       </c>
@@ -19782,7 +19775,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>855</v>
       </c>
@@ -19805,7 +19798,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>855</v>
       </c>
@@ -19828,7 +19821,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>875</v>
       </c>
@@ -19851,7 +19844,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>875</v>
       </c>
@@ -19874,7 +19867,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>875</v>
       </c>
@@ -19897,7 +19890,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>875</v>
       </c>
@@ -19920,7 +19913,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>900</v>
       </c>
@@ -19943,7 +19936,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>900</v>
       </c>
@@ -19966,7 +19959,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>900</v>
       </c>
@@ -19989,7 +19982,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>900</v>
       </c>
@@ -20012,7 +20005,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>920</v>
       </c>
@@ -20035,7 +20028,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>920</v>
       </c>
@@ -20058,7 +20051,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>920</v>
       </c>
@@ -20081,7 +20074,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>920</v>
       </c>
@@ -20104,7 +20097,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>943</v>
       </c>
@@ -20127,7 +20120,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>943</v>
       </c>
@@ -20150,7 +20143,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>943</v>
       </c>
@@ -20173,7 +20166,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>943</v>
       </c>
@@ -20196,7 +20189,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>965</v>
       </c>
@@ -20219,7 +20212,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>965</v>
       </c>
@@ -20242,7 +20235,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>965</v>
       </c>
@@ -20265,7 +20258,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>965</v>
       </c>
@@ -20288,7 +20281,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>989</v>
       </c>
@@ -20311,7 +20304,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>989</v>
       </c>
@@ -20334,7 +20327,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>989</v>
       </c>
@@ -20357,7 +20350,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>989</v>
       </c>
@@ -20380,7 +20373,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1012</v>
       </c>
@@ -20403,7 +20396,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1012</v>
       </c>
@@ -20426,7 +20419,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1012</v>
       </c>
@@ -20449,7 +20442,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1012</v>
       </c>
@@ -20472,7 +20465,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1037</v>
       </c>
@@ -20495,7 +20488,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1037</v>
       </c>
@@ -20518,7 +20511,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1037</v>
       </c>
@@ -20541,7 +20534,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1037</v>
       </c>
@@ -20564,7 +20557,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1058</v>
       </c>
@@ -20587,7 +20580,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1058</v>
       </c>
@@ -20610,7 +20603,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1058</v>
       </c>
@@ -20633,7 +20626,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1058</v>
       </c>
@@ -20656,7 +20649,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1083</v>
       </c>
@@ -20679,7 +20672,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1083</v>
       </c>
@@ -20702,7 +20695,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1083</v>
       </c>
@@ -20725,7 +20718,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1083</v>
       </c>
@@ -20748,7 +20741,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1103</v>
       </c>
@@ -20771,7 +20764,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1103</v>
       </c>
@@ -20794,7 +20787,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1103</v>
       </c>
@@ -20817,7 +20810,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1103</v>
       </c>
@@ -20840,7 +20833,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1127</v>
       </c>
@@ -20863,7 +20856,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1127</v>
       </c>
@@ -20886,7 +20879,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1127</v>
       </c>
@@ -20909,7 +20902,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1127</v>
       </c>
@@ -20932,7 +20925,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1148</v>
       </c>
@@ -20955,7 +20948,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1148</v>
       </c>
@@ -20978,7 +20971,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1148</v>
       </c>
@@ -21001,7 +20994,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1148</v>
       </c>
@@ -21024,7 +21017,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1167</v>
       </c>
@@ -21047,7 +21040,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1167</v>
       </c>
@@ -21070,7 +21063,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1167</v>
       </c>
@@ -21093,7 +21086,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1167</v>
       </c>
@@ -21116,7 +21109,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1186</v>
       </c>
@@ -21139,7 +21132,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1186</v>
       </c>
@@ -21162,7 +21155,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1186</v>
       </c>
@@ -21185,7 +21178,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1186</v>
       </c>
@@ -21208,7 +21201,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1204</v>
       </c>
@@ -21231,7 +21224,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1204</v>
       </c>
@@ -21254,7 +21247,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1204</v>
       </c>
@@ -21277,7 +21270,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1204</v>
       </c>
@@ -21300,7 +21293,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1226</v>
       </c>
@@ -21323,7 +21316,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1226</v>
       </c>
@@ -21346,7 +21339,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1226</v>
       </c>
@@ -21369,7 +21362,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1226</v>
       </c>
@@ -21392,7 +21385,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1250</v>
       </c>
@@ -21415,7 +21408,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1250</v>
       </c>
@@ -21438,7 +21431,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1250</v>
       </c>
@@ -21461,7 +21454,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1250</v>
       </c>
@@ -21484,7 +21477,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1270</v>
       </c>
@@ -21507,7 +21500,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1270</v>
       </c>
@@ -21530,7 +21523,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1270</v>
       </c>
@@ -21553,7 +21546,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1270</v>
       </c>
@@ -21576,7 +21569,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1290</v>
       </c>
@@ -21599,7 +21592,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1290</v>
       </c>
@@ -21622,7 +21615,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1290</v>
       </c>
@@ -21645,7 +21638,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1290</v>
       </c>
@@ -21668,7 +21661,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1312</v>
       </c>
@@ -21691,7 +21684,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1312</v>
       </c>
@@ -21714,7 +21707,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1312</v>
       </c>
@@ -21737,7 +21730,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1312</v>
       </c>
@@ -21760,7 +21753,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1333</v>
       </c>
@@ -21783,7 +21776,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1333</v>
       </c>
@@ -21806,7 +21799,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1333</v>
       </c>
@@ -21829,7 +21822,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1333</v>
       </c>
@@ -21852,7 +21845,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1353</v>
       </c>
@@ -21875,7 +21868,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1353</v>
       </c>
@@ -21898,7 +21891,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1353</v>
       </c>
@@ -21921,7 +21914,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1353</v>
       </c>
@@ -21944,7 +21937,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1374</v>
       </c>
@@ -21967,7 +21960,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1374</v>
       </c>
@@ -21990,7 +21983,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1374</v>
       </c>
@@ -22013,7 +22006,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1374</v>
       </c>
@@ -22036,7 +22029,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1396</v>
       </c>
@@ -22059,7 +22052,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1396</v>
       </c>
@@ -22082,7 +22075,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1396</v>
       </c>
@@ -22105,7 +22098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1396</v>
       </c>
@@ -22128,7 +22121,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1416</v>
       </c>
@@ -22151,7 +22144,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1416</v>
       </c>
@@ -22174,7 +22167,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1416</v>
       </c>
@@ -22197,7 +22190,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1416</v>
       </c>
@@ -22220,7 +22213,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1436</v>
       </c>
@@ -22243,7 +22236,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1436</v>
       </c>
@@ -22266,7 +22259,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1436</v>
       </c>
@@ -22289,7 +22282,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1436</v>
       </c>
@@ -22312,7 +22305,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1436</v>
       </c>
@@ -22335,7 +22328,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1436</v>
       </c>
@@ -22358,7 +22351,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1436</v>
       </c>
@@ -22381,7 +22374,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1436</v>
       </c>
@@ -22404,7 +22397,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1436</v>
       </c>
@@ -22427,7 +22420,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1436</v>
       </c>
@@ -22450,7 +22443,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1436</v>
       </c>
@@ -22473,7 +22466,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1436</v>
       </c>
@@ -22496,7 +22489,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1436</v>
       </c>
@@ -22519,7 +22512,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1436</v>
       </c>
@@ -22542,7 +22535,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1454</v>
       </c>
@@ -22565,7 +22558,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1454</v>
       </c>
@@ -22588,7 +22581,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1454</v>
       </c>
@@ -22611,7 +22604,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1454</v>
       </c>
@@ -22636,22 +22629,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="4" max="24" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="42.142857142857146" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22662,7 +22655,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -22673,7 +22666,7 @@
         <v>4850</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -22684,7 +22677,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -22695,7 +22688,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -22706,7 +22699,7 @@
         <v>9450</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -22717,7 +22710,7 @@
         <v>2910</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>204</v>
       </c>
@@ -22728,7 +22721,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>231</v>
       </c>
@@ -22736,7 +22729,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -22747,7 +22740,7 @@
         <v>4125</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>291</v>
       </c>
@@ -22755,7 +22748,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>320</v>
       </c>
@@ -22766,7 +22759,7 @@
         <v>7750</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>344</v>
       </c>
@@ -22777,7 +22770,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>372</v>
       </c>
@@ -22785,7 +22778,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>398</v>
       </c>
@@ -22796,7 +22789,7 @@
         <v>9980</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>427</v>
       </c>
@@ -22807,7 +22800,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>454</v>
       </c>
@@ -22815,7 +22808,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>479</v>
       </c>
@@ -22826,7 +22819,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>504</v>
       </c>
@@ -22837,7 +22830,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -22845,7 +22838,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>549</v>
       </c>
@@ -22856,7 +22849,7 @@
         <v>8640</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>578</v>
       </c>
@@ -22867,7 +22860,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>602</v>
       </c>
@@ -22878,7 +22871,7 @@
         <v>7425</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>627</v>
       </c>
@@ -22886,7 +22879,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>647</v>
       </c>
@@ -22897,7 +22890,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>672</v>
       </c>
@@ -22908,7 +22901,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>696</v>
       </c>
@@ -22916,7 +22909,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>718</v>
       </c>
@@ -22927,7 +22920,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>739</v>
       </c>
@@ -22938,7 +22931,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>761</v>
       </c>
@@ -22946,7 +22939,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>786</v>
       </c>
@@ -22957,7 +22950,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>812</v>
       </c>
@@ -22968,7 +22961,7 @@
         <v>8800</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>831</v>
       </c>
@@ -22976,7 +22969,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>855</v>
       </c>
@@ -22987,7 +22980,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>875</v>
       </c>
@@ -22998,7 +22991,7 @@
         <v>6750</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>900</v>
       </c>
@@ -23006,7 +22999,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>920</v>
       </c>
@@ -23017,7 +23010,7 @@
         <v>4525</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>943</v>
       </c>
@@ -23028,7 +23021,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>965</v>
       </c>
@@ -23036,7 +23029,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>989</v>
       </c>
@@ -23047,7 +23040,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1012</v>
       </c>
@@ -23058,7 +23051,7 @@
         <v>9180</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1037</v>
       </c>
@@ -23066,7 +23059,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1058</v>
       </c>
@@ -23077,7 +23070,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1083</v>
       </c>
@@ -23085,7 +23078,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1103</v>
       </c>
@@ -23096,7 +23089,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1127</v>
       </c>
@@ -23107,7 +23100,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1148</v>
       </c>
@@ -23115,7 +23108,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1167</v>
       </c>
@@ -23126,7 +23119,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1186</v>
       </c>
@@ -23137,7 +23130,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1204</v>
       </c>
@@ -23145,7 +23138,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1226</v>
       </c>
@@ -23156,7 +23149,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1250</v>
       </c>
@@ -23167,7 +23160,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1270</v>
       </c>
@@ -23175,7 +23168,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1290</v>
       </c>
@@ -23186,7 +23179,7 @@
         <v>6240</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1312</v>
       </c>
@@ -23197,7 +23190,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1333</v>
       </c>
@@ -23205,7 +23198,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1353</v>
       </c>
@@ -23216,7 +23209,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1374</v>
       </c>
@@ -23227,7 +23220,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1396</v>
       </c>
@@ -23235,7 +23228,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1416</v>
       </c>
@@ -23246,7 +23239,7 @@
         <v>7185</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1436</v>
       </c>
@@ -23257,7 +23250,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1454</v>
       </c>
@@ -23267,30 +23260,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L121"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.428571428571427" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.285714285714286" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="9.33203125" customWidth="1"/>
+    <col min="7" max="8" width="9.285714285714286" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
     <col min="11" max="11" width="29" customWidth="1"/>
-    <col min="12" max="12" width="42.109375" customWidth="1"/>
-    <col min="13" max="24" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="42.142857142857146" customWidth="1"/>
+    <col min="13" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -23328,7 +23321,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -23336,7 +23329,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -23374,7 +23367,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -23403,13 +23396,13 @@
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L4" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -23420,13 +23413,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="E5" t="s">
         <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="G5" t="s">
         <v>1126</v>
@@ -23441,13 +23434,13 @@
         <v>1871</v>
       </c>
       <c r="K5" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="L5" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -23455,7 +23448,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>146</v>
       </c>
@@ -23466,7 +23459,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="E7" t="s">
         <v>172</v>
@@ -23487,13 +23480,13 @@
         <v>1871</v>
       </c>
       <c r="K7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="L7" t="s">
         <v>1881</v>
       </c>
-      <c r="L7" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>146</v>
       </c>
@@ -23504,10 +23497,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="E8" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="F8" t="s">
         <v>1079</v>
@@ -23522,13 +23515,13 @@
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L8" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -23539,10 +23532,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="E9" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="F9" t="s">
         <v>414</v>
@@ -23560,13 +23553,13 @@
         <v>1871</v>
       </c>
       <c r="K9" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="L9" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -23574,7 +23567,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>204</v>
       </c>
@@ -23585,10 +23578,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="E11" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="F11" t="s">
         <v>1185</v>
@@ -23606,13 +23599,13 @@
         <v>1871</v>
       </c>
       <c r="K11" t="s">
+        <v>1890</v>
+      </c>
+      <c r="L11" t="s">
         <v>1889</v>
       </c>
-      <c r="L11" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>204</v>
       </c>
@@ -23623,7 +23616,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="E12" t="s">
         <v>729</v>
@@ -23641,13 +23634,13 @@
         <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L12" t="s">
-        <v>1891</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>204</v>
       </c>
@@ -23658,10 +23651,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="E13" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="F13" t="s">
         <v>230</v>
@@ -23679,13 +23672,13 @@
         <v>1871</v>
       </c>
       <c r="K13" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="L13" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>231</v>
       </c>
@@ -23693,7 +23686,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>263</v>
       </c>
@@ -23704,10 +23697,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="E15" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="F15" t="s">
         <v>564</v>
@@ -23725,13 +23718,13 @@
         <v>1871</v>
       </c>
       <c r="K15" t="s">
+        <v>1897</v>
+      </c>
+      <c r="L15" t="s">
         <v>1896</v>
       </c>
-      <c r="L15" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>263</v>
       </c>
@@ -23742,10 +23735,10 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="E16" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="F16" t="s">
         <v>202</v>
@@ -23760,13 +23753,13 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L16" t="s">
         <v>1900</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>263</v>
       </c>
@@ -23804,7 +23797,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>291</v>
       </c>
@@ -23812,7 +23805,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>320</v>
       </c>
@@ -23850,7 +23843,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>320</v>
       </c>
@@ -23879,13 +23872,13 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L20" t="s">
         <v>1909</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>320</v>
       </c>
@@ -23923,7 +23916,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>344</v>
       </c>
@@ -23931,7 +23924,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>372</v>
       </c>
@@ -23969,7 +23962,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>372</v>
       </c>
@@ -23998,13 +23991,13 @@
         <v>2</v>
       </c>
       <c r="J24" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L24" t="s">
         <v>1920</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>372</v>
       </c>
@@ -24042,7 +24035,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>398</v>
       </c>
@@ -24050,7 +24043,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>427</v>
       </c>
@@ -24088,7 +24081,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>427</v>
       </c>
@@ -24126,7 +24119,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>427</v>
       </c>
@@ -24164,7 +24157,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>454</v>
       </c>
@@ -24172,18 +24165,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>479</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>479</v>
       </c>
@@ -24221,7 +24214,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>479</v>
       </c>
@@ -24259,7 +24252,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>504</v>
       </c>
@@ -24267,7 +24260,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>526</v>
       </c>
@@ -24305,7 +24298,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>526</v>
       </c>
@@ -24343,7 +24336,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>526</v>
       </c>
@@ -24381,7 +24374,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>549</v>
       </c>
@@ -24389,18 +24382,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>578</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>578</v>
       </c>
@@ -24438,7 +24431,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>578</v>
       </c>
@@ -24476,7 +24469,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>602</v>
       </c>
@@ -24484,7 +24477,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>627</v>
       </c>
@@ -24522,7 +24515,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>627</v>
       </c>
@@ -24560,7 +24553,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>627</v>
       </c>
@@ -24574,7 +24567,7 @@
         <v>1967</v>
       </c>
       <c r="E45" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="F45" t="s">
         <v>1239</v>
@@ -24598,7 +24591,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>647</v>
       </c>
@@ -24606,7 +24599,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>672</v>
       </c>
@@ -24644,7 +24637,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>672</v>
       </c>
@@ -24682,7 +24675,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>672</v>
       </c>
@@ -24720,7 +24713,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>696</v>
       </c>
@@ -24728,7 +24721,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>718</v>
       </c>
@@ -24766,7 +24759,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>718</v>
       </c>
@@ -24804,7 +24797,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>718</v>
       </c>
@@ -24842,7 +24835,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>739</v>
       </c>
@@ -24850,7 +24843,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>761</v>
       </c>
@@ -24888,7 +24881,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>761</v>
       </c>
@@ -24926,7 +24919,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>761</v>
       </c>
@@ -24964,7 +24957,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>786</v>
       </c>
@@ -24972,7 +24965,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>812</v>
       </c>
@@ -25010,7 +25003,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>812</v>
       </c>
@@ -25048,7 +25041,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>812</v>
       </c>
@@ -25086,7 +25079,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>831</v>
       </c>
@@ -25094,7 +25087,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>855</v>
       </c>
@@ -25132,7 +25125,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>855</v>
       </c>
@@ -25170,7 +25163,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>855</v>
       </c>
@@ -25208,7 +25201,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>875</v>
       </c>
@@ -25216,7 +25209,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>900</v>
       </c>
@@ -25254,7 +25247,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>900</v>
       </c>
@@ -25292,7 +25285,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>900</v>
       </c>
@@ -25330,7 +25323,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>920</v>
       </c>
@@ -25338,18 +25331,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>943</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>943</v>
       </c>
@@ -25387,7 +25380,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>943</v>
       </c>
@@ -25425,7 +25418,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>965</v>
       </c>
@@ -25433,7 +25426,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>989</v>
       </c>
@@ -25471,7 +25464,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>989</v>
       </c>
@@ -25509,7 +25502,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>989</v>
       </c>
@@ -25547,7 +25540,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1012</v>
       </c>
@@ -25555,18 +25548,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1037</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1037</v>
       </c>
@@ -25604,7 +25597,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>1037</v>
       </c>
@@ -25642,7 +25635,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1058</v>
       </c>
@@ -25650,7 +25643,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>1083</v>
       </c>
@@ -25664,7 +25657,7 @@
         <v>1967</v>
       </c>
       <c r="E83" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="F83" t="s">
         <v>692</v>
@@ -25688,7 +25681,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1083</v>
       </c>
@@ -25726,7 +25719,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1083</v>
       </c>
@@ -25764,7 +25757,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1103</v>
       </c>
@@ -25772,7 +25765,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1127</v>
       </c>
@@ -25810,7 +25803,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1127</v>
       </c>
@@ -25848,7 +25841,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1127</v>
       </c>
@@ -25886,7 +25879,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1148</v>
       </c>
@@ -25894,7 +25887,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1167</v>
       </c>
@@ -25932,7 +25925,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1167</v>
       </c>
@@ -25970,7 +25963,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1167</v>
       </c>
@@ -26008,7 +26001,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1186</v>
       </c>
@@ -26016,7 +26009,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1204</v>
       </c>
@@ -26054,7 +26047,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1204</v>
       </c>
@@ -26092,7 +26085,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1204</v>
       </c>
@@ -26130,7 +26123,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1226</v>
       </c>
@@ -26138,7 +26131,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1250</v>
       </c>
@@ -26176,7 +26169,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1250</v>
       </c>
@@ -26214,7 +26207,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1250</v>
       </c>
@@ -26252,7 +26245,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1270</v>
       </c>
@@ -26260,7 +26253,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1290</v>
       </c>
@@ -26298,7 +26291,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1290</v>
       </c>
@@ -26336,7 +26329,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1290</v>
       </c>
@@ -26365,13 +26358,13 @@
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L105" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1312</v>
       </c>
@@ -26379,18 +26372,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1333</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1333</v>
       </c>
@@ -26428,7 +26421,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1333</v>
       </c>
@@ -26457,13 +26450,13 @@
         <v>2</v>
       </c>
       <c r="J109" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L109" t="s">
         <v>2118</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1353</v>
       </c>
@@ -26471,7 +26464,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1374</v>
       </c>
@@ -26509,7 +26502,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1374</v>
       </c>
@@ -26547,7 +26540,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1374</v>
       </c>
@@ -26576,13 +26569,13 @@
         <v>4</v>
       </c>
       <c r="J113" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L113" t="s">
         <v>2128</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1396</v>
       </c>
@@ -26590,18 +26583,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1416</v>
       </c>
       <c r="B115" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1416</v>
       </c>
@@ -26639,7 +26632,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1416</v>
       </c>
@@ -26668,13 +26661,13 @@
         <v>2</v>
       </c>
       <c r="J117" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L117" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1436</v>
       </c>
@@ -26682,7 +26675,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1454</v>
       </c>
@@ -26711,13 +26704,13 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L119" t="s">
         <v>2137</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1454</v>
       </c>
@@ -26755,7 +26748,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1454</v>
       </c>
@@ -26784,7 +26777,7 @@
         <v>2</v>
       </c>
       <c r="J121" t="s">
-        <v>1899</v>
+        <v>1876</v>
       </c>
       <c r="L121" t="s">
         <v>2145</v>
@@ -26792,22 +26785,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="8" width="42.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
+    <col min="2" max="8" width="42.142857142857146" customWidth="1"/>
     <col min="9" max="11" width="21" customWidth="1"/>
-    <col min="12" max="24" width="13.5546875" customWidth="1"/>
+    <col min="12" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -26842,7 +26835,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -26874,7 +26867,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -26903,7 +26896,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -26938,7 +26931,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -26970,7 +26963,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -26999,7 +26992,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>204</v>
       </c>
@@ -27031,7 +27024,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>231</v>
       </c>
@@ -27063,7 +27056,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -27092,7 +27085,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>291</v>
       </c>
@@ -27127,7 +27120,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>320</v>
       </c>
@@ -27159,7 +27152,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>344</v>
       </c>
@@ -27191,7 +27184,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>372</v>
       </c>
@@ -27220,7 +27213,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>398</v>
       </c>
@@ -27255,7 +27248,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>427</v>
       </c>
@@ -27287,7 +27280,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>454</v>
       </c>
@@ -27322,7 +27315,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>479</v>
       </c>
@@ -27351,7 +27344,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>504</v>
       </c>
@@ -27383,7 +27376,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -27412,7 +27405,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>549</v>
       </c>
@@ -27447,7 +27440,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>578</v>
       </c>
@@ -27476,7 +27469,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>602</v>
       </c>
@@ -27505,7 +27498,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>627</v>
       </c>
@@ -27537,7 +27530,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>647</v>
       </c>
@@ -27566,7 +27559,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>672</v>
       </c>
@@ -27598,7 +27591,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>696</v>
       </c>
@@ -27633,7 +27626,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>718</v>
       </c>
@@ -27662,7 +27655,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>739</v>
       </c>
@@ -27697,7 +27690,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>761</v>
       </c>
@@ -27729,7 +27722,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>786</v>
       </c>
@@ -27758,7 +27751,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>812</v>
       </c>
@@ -27790,7 +27783,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>831</v>
       </c>
@@ -27819,7 +27812,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>855</v>
       </c>
@@ -27854,7 +27847,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>875</v>
       </c>
@@ -27886,7 +27879,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>900</v>
       </c>
@@ -27915,7 +27908,7 @@
         <v>2341</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>920</v>
       </c>
@@ -27950,7 +27943,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>943</v>
       </c>
@@ -27979,7 +27972,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>965</v>
       </c>
@@ -28011,7 +28004,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>989</v>
       </c>
@@ -28043,7 +28036,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1012</v>
       </c>
@@ -28072,7 +28065,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1037</v>
       </c>
@@ -28107,7 +28100,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1058</v>
       </c>
@@ -28139,7 +28132,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1083</v>
       </c>
@@ -28168,7 +28161,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1103</v>
       </c>
@@ -28203,7 +28196,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1127</v>
       </c>
@@ -28235,7 +28228,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1148</v>
       </c>
@@ -28264,7 +28257,7 @@
         <v>2382</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1167</v>
       </c>
@@ -28296,7 +28289,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1186</v>
       </c>
@@ -28331,7 +28324,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1204</v>
       </c>
@@ -28360,7 +28353,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1226</v>
       </c>
@@ -28392,7 +28385,7 @@
         <v>2409</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1250</v>
       </c>
@@ -28427,7 +28420,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1270</v>
       </c>
@@ -28456,7 +28449,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1290</v>
       </c>
@@ -28488,7 +28481,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1312</v>
       </c>
@@ -28520,7 +28513,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1333</v>
       </c>
@@ -28549,7 +28542,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1353</v>
       </c>
@@ -28581,7 +28574,7 @@
         <v>2436</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1374</v>
       </c>
@@ -28613,7 +28606,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1396</v>
       </c>
@@ -28648,7 +28641,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1416</v>
       </c>
@@ -28677,7 +28670,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1436</v>
       </c>
@@ -28709,7 +28702,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1454</v>
       </c>
@@ -28746,21 +28739,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="24" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
+    <col min="2" max="2" width="20.714285714285715" customWidth="1"/>
+    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2461</v>
       </c>
@@ -28768,7 +28761,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -28776,7 +28769,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -28784,7 +28777,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -28792,7 +28785,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -28800,7 +28793,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -28808,7 +28801,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>204</v>
       </c>
@@ -28816,7 +28809,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>231</v>
       </c>
@@ -28824,7 +28817,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -28832,7 +28825,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>291</v>
       </c>
@@ -28840,7 +28833,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>320</v>
       </c>
@@ -28848,7 +28841,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>344</v>
       </c>
@@ -28856,7 +28849,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>372</v>
       </c>
@@ -28864,7 +28857,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>398</v>
       </c>
@@ -28872,7 +28865,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>427</v>
       </c>
@@ -28880,7 +28873,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>454</v>
       </c>
@@ -28888,7 +28881,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>479</v>
       </c>
@@ -28896,7 +28889,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>504</v>
       </c>
@@ -28904,7 +28897,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -28912,7 +28905,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>549</v>
       </c>
@@ -28920,7 +28913,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>578</v>
       </c>
@@ -28928,7 +28921,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>602</v>
       </c>
@@ -28936,7 +28929,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>627</v>
       </c>
@@ -28944,7 +28937,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>647</v>
       </c>
@@ -28952,7 +28945,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>672</v>
       </c>
@@ -28960,15 +28953,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>696</v>
       </c>
       <c r="B26" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>718</v>
       </c>
@@ -28976,7 +28969,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>739</v>
       </c>
@@ -28984,7 +28977,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>761</v>
       </c>
@@ -28992,7 +28985,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>786</v>
       </c>
@@ -29000,7 +28993,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>812</v>
       </c>
@@ -29008,7 +29001,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>831</v>
       </c>
@@ -29016,7 +29009,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>855</v>
       </c>
@@ -29024,7 +29017,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>875</v>
       </c>
@@ -29032,7 +29025,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>900</v>
       </c>
@@ -29040,7 +29033,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>920</v>
       </c>
@@ -29048,7 +29041,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>943</v>
       </c>
@@ -29056,7 +29049,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>965</v>
       </c>
@@ -29064,7 +29057,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>989</v>
       </c>
@@ -29072,7 +29065,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1012</v>
       </c>
@@ -29080,7 +29073,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1037</v>
       </c>
@@ -29088,7 +29081,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1058</v>
       </c>
@@ -29096,7 +29089,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1083</v>
       </c>
@@ -29104,7 +29097,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1103</v>
       </c>
@@ -29112,7 +29105,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1127</v>
       </c>
@@ -29120,7 +29113,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1148</v>
       </c>
@@ -29128,7 +29121,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1167</v>
       </c>
@@ -29136,7 +29129,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1186</v>
       </c>
@@ -29144,7 +29137,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1204</v>
       </c>
@@ -29152,7 +29145,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1226</v>
       </c>
@@ -29160,7 +29153,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1250</v>
       </c>
@@ -29168,7 +29161,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1270</v>
       </c>
@@ -29176,7 +29169,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1290</v>
       </c>
@@ -29184,7 +29177,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1312</v>
       </c>
@@ -29192,7 +29185,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1333</v>
       </c>
@@ -29200,7 +29193,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1353</v>
       </c>
@@ -29208,7 +29201,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1374</v>
       </c>
@@ -29216,7 +29209,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1396</v>
       </c>
@@ -29224,7 +29217,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1416</v>
       </c>
@@ -29232,7 +29225,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1436</v>
       </c>
@@ -29240,7 +29233,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1454</v>
       </c>
@@ -29250,6 +29243,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>